--- a/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
+++ b/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
@@ -716,50 +716,50 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
+          <t>HĐTN
+(Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Âm nhạc
 (Tươi (Âm nhạc))</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>TC Toán
-(Nhật (GVCN 4B))</t>
+          <t>Công nghệ
+(Hiền)</t>
         </is>
       </c>
       <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>Khoa học
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TC Tiếng Việt
 (Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 (Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Tự nhiên &amp; Xã hội
 (Phượng)</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TC Toán
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Công nghệ
 (Hiền)</t>
         </is>
       </c>
@@ -815,13 +815,13 @@
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Đạo đức
+(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Tiếng Việt
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -836,50 +836,50 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
           <t>TC Tiếng Việt
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+(Lập)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga (Tin học))</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Khoa học
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
@@ -903,8 +903,8 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 (Thúy (GVCN 2A))</t>
         </is>
       </c>
@@ -927,32 +927,32 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
           <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Lan (GVCN 4A))</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
+          <t>Tiếng Việt
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Khoa học
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
         </is>
       </c>
     </row>
@@ -966,56 +966,56 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
           <t>GDTC
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+(Hà)</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>Tin học
+(Nga (Tin học))</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>LS &amp; ĐL
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
         </is>
       </c>
     </row>
@@ -1029,127 +1029,127 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
+          <t>GDTC
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
+(Tấm (GDTC))</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Tiết 1</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 (Thúy (GVCN 2A))</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
 (Lập)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Khoa học
 (Hiền)</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
 (Thanh (GVCN 5A))</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Thứ 3</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Tiết 1</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>Công nghệ
-(Hiền)</t>
-        </is>
-      </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
         </is>
       </c>
     </row>
@@ -1163,37 +1163,37 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
           <t>Tự nhiên &amp; Xã hội
 (Phượng)</t>
         </is>
       </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
+        </is>
+      </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Lập)</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>LS &amp; ĐL
 (Hiền)</t>
         </is>
       </c>
@@ -1238,14 +1238,14 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Hà)</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -1262,20 +1262,20 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>LS &amp; ĐL
+(Hiền)</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>TC Tiếng Việt
+(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>Công nghệ
-(Hiền)</t>
+          <t>Tiếng Việt
+(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -1289,43 +1289,43 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
+          <t>TC Toán
 (Phượng)</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Lập)</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
           <t>Toán
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>Đạo đức
 (Lan (GVCN 4A))</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
+          <t>Khoa học
 (Hiền)</t>
         </is>
       </c>
@@ -1337,8 +1337,8 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Tiếng Việt
+(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -1362,50 +1362,50 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Phượng)</t>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
+          <t>Toán
+(Thúy (GVCN 2A))</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
+          <t>Tiếng Việt
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Khoa học
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>Toán
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -1419,44 +1419,44 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+          <t>Đạo đức
+(Phượng)</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>HĐTN
-(Thúy (GVCN 2A))</t>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 (Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Công nghệ
+(Lập)</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+          <t>GDTC
+(Tấm (GDTC))</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>TC Tiếng Việt
+(Nhật (GVCN 4B))</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -1467,8 +1467,8 @@
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+          <t>Khoa học
+(Hiền)</t>
         </is>
       </c>
     </row>
@@ -1482,126 +1482,126 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Phượng)</t>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Toán
+(Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>Đạo đức
+(Vũ Hương (GVCN 5B))</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Tiết 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
+(Hà)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Toán
 (Chiên (GVCN 2B))</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
+(Tấm (GDTC))</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Toán
 (Nhật (GVCN 4B))</t>
         </is>
       </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Toán
 (Thanh (GVCN 5A))</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Thứ 4</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Tiết 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>LS &amp; ĐL
 (Hiền)</t>
         </is>
       </c>
@@ -1622,8 +1622,8 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -1634,37 +1634,37 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
+          <t>TC Toán
+(Lập)</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Tiếng Việt
+(Lan (GVCN 4A))</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Tiếng Việt
+(Nhật (GVCN 4B))</t>
         </is>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>HĐTN
 (Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -1679,14 +1679,14 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Đạo đức
+(Phượng)</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Phượng)</t>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -1696,39 +1696,39 @@
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga (Tin học))</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>Công nghệ
+(Hiền)</t>
         </is>
       </c>
     </row>
@@ -1742,14 +1742,14 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>TC Toán
+(Phượng)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Phượng)</t>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -1760,38 +1760,38 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>TTCM
+          <t>Toán
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 (Lan (GVCN 4A))</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>Khoa học
+(Hiền)</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>Tin học
-(Nga (Tin học))</t>
         </is>
       </c>
     </row>
@@ -1809,55 +1809,55 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 (Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+(Lan (GVCN 4A))</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Khoa học
-(Hiền)</t>
+          <t>GDTC
+(Tấm (GDTC))</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
           <t>TC Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -1878,44 +1878,44 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Phượng)</t>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>GDTC
+(Hà)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>GDTC
 (Tấm (GDTC))</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LS &amp; ĐL
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
@@ -1935,114 +1935,114 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Đạo đức
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Lập)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>LS &amp; ĐL
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Vũ Hương (GVCN 5B))</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Tiết 1</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
           <t>GDTC
 (Phượng)</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
 (Thúy (GVCN 2A))</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Đạo đức
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Thứ 5</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Tiết 1</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>TC Tiếng Việt
 (Lập)</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
-          <t>TTCM
+          <t>Tiếng Việt
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 (Nhật (GVCN 4B))</t>
         </is>
       </c>
@@ -2054,8 +2054,8 @@
       </c>
       <c r="L26" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>HĐTN
+(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -2069,56 +2069,56 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>TC Tiếng Việt
+(Phượng)</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
           <t>TC Toán
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+(Lập)</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 (Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
       <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
         <is>
           <t>Khoa học
 (Hiền)</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -2132,55 +2132,55 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>TC Toán
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Lập)</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>LS &amp; ĐL
+(Hiền)</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
+          <t>Đạo đức
 (Nhật (GVCN 4B))</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Khoa học
-(Hiền)</t>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -2201,50 +2201,50 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Toán
-(Hà Hương (GVCN 1B))</t>
+          <t>TC Toán
+(Phượng)</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga (Tin học))</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Nhật (GVCN 4B))</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh (GVCN 5A))</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>Công nghệ
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -2280,26 +2280,26 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Lập)</t>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Khoa học
-(Hiền)</t>
+          <t>Toán
+(Nhật (GVCN 4B))</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -2325,56 +2325,56 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
+(Hà)</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Đạo đức
+(Lập)</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>Toán
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Công nghệ
-(Hiền)</t>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>TC Toán
-(Vũ Hương (GVCN 5B))</t>
+          <t>Tin học
+(Nga (Tin học))</t>
         </is>
       </c>
     </row>
@@ -2388,111 +2388,111 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Hà Hương (GVCN 1B))</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Nhiên(GVCN 3A))</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan (GVCN 4A))</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 (Nõn (Anh))</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>LS &amp; ĐL
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
+(Tấm (GDTC))</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Tiết 1</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
 (Hà Hương (GVCN 1B))</t>
         </is>
       </c>
-      <c r="F32" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy (GVCN 2A))</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên (GVCN 2B))</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>HĐTN
 (Nhiên(GVCN 3A))</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Toán
 (Lan (GVCN 4A))</t>
         </is>
       </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Thứ 6</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Tiết 1</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>TTCM
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
@@ -2501,13 +2501,13 @@
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>TC Toán
+          <t>TC Tiếng Việt
 (Phượng)</t>
         </is>
       </c>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 (Thúy (GVCN 2A))</t>
         </is>
       </c>
@@ -2552,8 +2552,8 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
+          <t>Tiếng Anh
+(Nõn (Anh))</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
@@ -2564,14 +2564,14 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Toán
+(Thanh (GVCN 5A))</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
+          <t>Mỹ thuật
+(Việt (Mỹ thuật))</t>
         </is>
       </c>
     </row>
@@ -2585,16 +2585,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
+          <t>Toán
+(Đỗ Hương (GVCN 1A))</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -2609,8 +2609,8 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Tiếng Việt
+(Nhiên(GVCN 3A))</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
@@ -2621,19 +2621,19 @@
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Tiếng Việt
+(Nhật (GVCN 4B))</t>
         </is>
       </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
+          <t>Công nghệ
+(Hiền)</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TC Toán
 (Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
@@ -3130,50 +3130,50 @@
           <t>1A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>1B - HĐTN</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
           <t>2B - Toán</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>4B - TC Toán</t>
-        </is>
-      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
       <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O6" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="10" t="inlineStr"/>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>5A - Khoa học</t>
+          <t>4B - Công nghệ</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
+          <t>5A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R6" s="10" t="inlineStr"/>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>2A - Âm nhạc</t>
+          <t>4A - Âm nhạc</t>
         </is>
       </c>
       <c r="T6" s="10" t="inlineStr"/>
@@ -3191,23 +3191,19 @@
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Việt</t>
+          <t>1A - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>1B - Tiếng Việt</t>
+          <t>1B - Toán</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>3A - Tiếng Việt</t>
+          <t>3A - TC Toán</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr"/>
@@ -3216,26 +3212,30 @@
           <t>4B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>5A - Đạo đức</t>
+        </is>
+      </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>5B - HĐTN</t>
+          <t>5B - Tiếng Việt</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>2A - Tự nhiên &amp; Xã hội</t>
+          <t>2B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O7" s="10" t="inlineStr"/>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>4A - Khoa học</t>
+          <t>4A - Công nghệ</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Anh</t>
+          <t>2A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R7" s="10" t="inlineStr"/>
@@ -3252,50 +3252,46 @@
           <t>Tiết 4</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>2A - GDTC</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>3A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>4B - Toán</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>4A - Toán</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="inlineStr"/>
       <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>1A - TC Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Toán</t>
+          <t>2A - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>4A - LS &amp; ĐL</t>
+          <t>5A - Khoa học</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>1B - Tiếng Anh</t>
+          <t>4B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R8" s="10" t="inlineStr">
@@ -3305,7 +3301,11 @@
       </c>
       <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>3A - Tin học</t>
+        </is>
+      </c>
       <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3321,15 +3321,11 @@
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E9" s="10" t="inlineStr"/>
       <c r="F9" s="10" t="inlineStr"/>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>2A - Tiếng Việt</t>
+          <t>2A - Toán</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -3337,12 +3333,24 @@
           <t>2B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>4A - TC Toán</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Việt</t>
+          <t>5A - Toán</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr"/>
@@ -3351,27 +3359,19 @@
           <t>1B - TC Tiếng Việt</t>
         </is>
       </c>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>3A - TC Toán</t>
-        </is>
-      </c>
+      <c r="O9" s="10" t="inlineStr"/>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>4B - LS &amp; ĐL</t>
+          <t>5B - Khoa học</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
+          <t>1A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R9" s="10" t="inlineStr"/>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>5B - Âm nhạc</t>
-        </is>
-      </c>
+      <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
       <c r="U9" s="10" t="inlineStr"/>
       <c r="V9" s="10" t="inlineStr"/>
@@ -3384,13 +3384,17 @@
           <t>Tiết 6</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>2B - GDTC</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
@@ -3399,45 +3403,41 @@
       <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>3A - TC Toán</t>
+          <t>3A - Toán</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr"/>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M10" s="10" t="inlineStr"/>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>1A - GDTC</t>
+          <t>1B - TC Toán</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr"/>
       <c r="P10" s="10" t="inlineStr">
         <is>
-          <t>5A - LS &amp; ĐL</t>
+          <t>5B - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>2B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>4A - GDTC</t>
-        </is>
-      </c>
+          <t>4A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr"/>
       <c r="S10" s="10" t="inlineStr"/>
-      <c r="T10" s="10" t="inlineStr">
-        <is>
-          <t>5B - Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="U10" s="10" t="inlineStr"/>
+      <c r="T10" s="10" t="inlineStr"/>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tin học</t>
+        </is>
+      </c>
       <c r="V10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3452,54 +3452,54 @@
       <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>1B - Toán</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>2A - Toán</t>
-        </is>
-      </c>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
       <c r="H11" s="10" t="inlineStr"/>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>3A - Toán</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>5A - Đạo đức</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr"/>
+          <t>3A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>4A - HĐTN</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>4B - Toán</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr"/>
+      <c r="M11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>1A - GDTC</t>
+        </is>
+      </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr">
-        <is>
-          <t>4A - Khoa học</t>
-        </is>
-      </c>
+          <t>2B - TC Toán</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr"/>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Anh</t>
+          <t>5B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R11" s="10" t="inlineStr">
         <is>
-          <t>4B - GDTC</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr"/>
+          <t>5A - GDTC</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>2A - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T11" s="10" t="inlineStr"/>
       <c r="U11" s="10" t="inlineStr"/>
       <c r="V11" s="10" t="inlineStr"/>
@@ -3520,57 +3520,57 @@
           <t>Tiết 1</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>2B - GDTC</t>
-        </is>
-      </c>
+      <c r="D12" s="13" t="inlineStr"/>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>1A - HĐTN</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>1B - TC Tiếng Việt</t>
-        </is>
-      </c>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr"/>
       <c r="G12" s="13" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>4A - HĐTN</t>
-        </is>
-      </c>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr"/>
-      <c r="M12" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N12" s="13" t="inlineStr"/>
-      <c r="O12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>5A - TC Toán</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>3A - TC Toán</t>
+        </is>
+      </c>
       <c r="P12" s="13" t="inlineStr">
         <is>
-          <t>5A - Công nghệ</t>
-        </is>
-      </c>
-      <c r="Q12" s="13" t="inlineStr"/>
+          <t>4A - Khoa học</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Anh</t>
+        </is>
+      </c>
       <c r="R12" s="13" t="inlineStr"/>
-      <c r="S12" s="13" t="inlineStr"/>
+      <c r="S12" s="13" t="inlineStr">
+        <is>
+          <t>5B - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T12" s="13" t="inlineStr">
         <is>
-          <t>4B - Mỹ thuật</t>
+          <t>1B - Mỹ thuật</t>
         </is>
       </c>
       <c r="U12" s="13" t="inlineStr"/>
@@ -3585,27 +3585,15 @@
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>1A - TC Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E13" s="13" t="inlineStr"/>
       <c r="F13" s="13" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="G13" s="13" t="inlineStr"/>
       <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="I13" s="13" t="inlineStr"/>
       <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="13" t="inlineStr"/>
       <c r="L13" s="13" t="inlineStr">
@@ -3620,23 +3608,35 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>2B - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr"/>
+          <t>1A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>3A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
       <c r="P13" s="13" t="inlineStr">
         <is>
-          <t>4A - Công nghệ</t>
-        </is>
-      </c>
-      <c r="Q13" s="13" t="inlineStr"/>
+          <t>4A - LS &amp; ĐL</t>
+        </is>
+      </c>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Anh</t>
+        </is>
+      </c>
       <c r="R13" s="13" t="inlineStr">
         <is>
           <t>4B - GDTC</t>
         </is>
       </c>
       <c r="S13" s="13" t="inlineStr"/>
-      <c r="T13" s="13" t="inlineStr"/>
+      <c r="T13" s="13" t="inlineStr">
+        <is>
+          <t>2B - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U13" s="13" t="inlineStr"/>
       <c r="V13" s="13" t="inlineStr"/>
     </row>
@@ -3648,11 +3648,7 @@
           <t>Tiết 3</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>2A - GDTC</t>
-        </is>
-      </c>
+      <c r="D14" s="13" t="inlineStr"/>
       <c r="E14" s="13" t="inlineStr">
         <is>
           <t>1A - Toán</t>
@@ -3675,33 +3671,37 @@
           <t>4A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L14" s="13" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr"/>
-      <c r="N14" s="13" t="inlineStr"/>
-      <c r="O14" s="13" t="inlineStr">
-        <is>
-          <t>2B - TC Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>5A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O14" s="13" t="inlineStr"/>
       <c r="P14" s="13" t="inlineStr">
         <is>
-          <t>5B - Công nghệ</t>
-        </is>
-      </c>
-      <c r="Q14" s="13" t="inlineStr"/>
+          <t>4B - LS &amp; ĐL</t>
+        </is>
+      </c>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Anh</t>
+        </is>
+      </c>
       <c r="R14" s="13" t="inlineStr"/>
       <c r="S14" s="13" t="inlineStr"/>
       <c r="T14" s="13" t="inlineStr"/>
-      <c r="U14" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tin học</t>
-        </is>
-      </c>
+      <c r="U14" s="13" t="inlineStr"/>
       <c r="V14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
@@ -3714,57 +3714,57 @@
       </c>
       <c r="D15" s="13" t="inlineStr"/>
       <c r="E15" s="13" t="inlineStr"/>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>1B - Toán</t>
-        </is>
-      </c>
+      <c r="F15" s="13" t="inlineStr"/>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>2A - Toán</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>2A - HĐTN</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
       <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>4A - Đạo đức</t>
+          <t>4A - Toán</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>1A - Tự nhiên &amp; Xã hội</t>
+          <t>1A - TC Toán</t>
         </is>
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>3A - TC Toán</t>
+          <t>2B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr">
         <is>
-          <t>4B - LS &amp; ĐL</t>
-        </is>
-      </c>
-      <c r="Q15" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Anh</t>
-        </is>
-      </c>
+          <t>4B - Khoa học</t>
+        </is>
+      </c>
+      <c r="Q15" s="13" t="inlineStr"/>
       <c r="R15" s="13" t="inlineStr">
         <is>
           <t>5A - GDTC</t>
         </is>
       </c>
-      <c r="S15" s="13" t="inlineStr"/>
-      <c r="T15" s="13" t="inlineStr"/>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>1B - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
+          <t>3A - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U15" s="13" t="inlineStr"/>
       <c r="V15" s="13" t="inlineStr"/>
     </row>
@@ -3786,53 +3786,53 @@
           <t>1A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
-      <c r="H16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>2A - Toán</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>3A - TC Tiếng Việt</t>
+          <t>3A - Tiếng Việt</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr"/>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>1B - GDTC</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>2A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P16" s="13" t="inlineStr"/>
+          <t>4B - Toán</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="13" t="inlineStr"/>
+      <c r="O16" s="13" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t>4A - Khoa học</t>
+        </is>
+      </c>
       <c r="Q16" s="13" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
+          <t>5B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R16" s="13" t="inlineStr"/>
-      <c r="S16" s="13" t="inlineStr">
-        <is>
-          <t>2B - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T16" s="13" t="inlineStr">
-        <is>
-          <t>5A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="S16" s="13" t="inlineStr"/>
+      <c r="T16" s="13" t="inlineStr"/>
       <c r="U16" s="13" t="inlineStr"/>
       <c r="V16" s="13" t="inlineStr"/>
     </row>
@@ -3845,59 +3845,59 @@
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>2A - HĐTN</t>
-        </is>
-      </c>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>2B - Toán</t>
+          <t>2B - Tiếng Việt</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>4B - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
           <t>5A - Toán</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>5B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N17" s="13" t="inlineStr"/>
-      <c r="O17" s="13" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
-      <c r="Q17" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R17" s="13" t="inlineStr"/>
-      <c r="S17" s="13" t="inlineStr"/>
-      <c r="T17" s="13" t="inlineStr"/>
-      <c r="U17" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tin học</t>
-        </is>
-      </c>
+      <c r="M17" s="13" t="inlineStr"/>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>1B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>3A - Công nghệ</t>
+        </is>
+      </c>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>5B - Khoa học</t>
+        </is>
+      </c>
+      <c r="Q17" s="13" t="inlineStr"/>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>4A - GDTC</t>
+        </is>
+      </c>
+      <c r="S17" s="13" t="inlineStr">
+        <is>
+          <t>1A - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T17" s="13" t="inlineStr">
+        <is>
+          <t>2A - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U17" s="13" t="inlineStr"/>
       <c r="V17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
@@ -3909,58 +3909,58 @@
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>1B - Toán</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr"/>
+          <t>2B - Toán</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>4A - Toán</t>
+          <t>4A - Tiếng Việt</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>4B - Toán</t>
-        </is>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>5A - TC Toán</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="13" t="inlineStr">
-        <is>
-          <t>1A - Đạo đức</t>
-        </is>
-      </c>
+          <t>4B - TC Toán</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>5B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr"/>
       <c r="O18" s="13" t="inlineStr"/>
       <c r="P18" s="13" t="inlineStr"/>
       <c r="Q18" s="13" t="inlineStr">
         <is>
-          <t>2A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R18" s="13" t="inlineStr">
-        <is>
-          <t>5B - GDTC</t>
-        </is>
-      </c>
-      <c r="S18" s="13" t="inlineStr">
-        <is>
-          <t>3A - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T18" s="13" t="inlineStr">
-        <is>
-          <t>1B - Mỹ thuật</t>
-        </is>
-      </c>
+          <t>5A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr"/>
+      <c r="S18" s="13" t="inlineStr"/>
+      <c r="T18" s="13" t="inlineStr"/>
       <c r="U18" s="13" t="inlineStr"/>
       <c r="V18" s="13" t="inlineStr"/>
     </row>
@@ -3980,41 +3980,45 @@
           <t>Tiết 1</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>2A - GDTC</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>1A - Toán</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>2B - Toán</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr"/>
       <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="10" t="inlineStr">
         <is>
           <t>4B - Toán</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>5A - Toán</t>
+        </is>
+      </c>
       <c r="M19" s="10" t="inlineStr"/>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>2A - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>2B - TC Tiếng Việt</t>
-        </is>
-      </c>
+          <t>1B - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="inlineStr"/>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>5B - Khoa học</t>
+          <t>5B - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -4022,17 +4026,13 @@
           <t>4A - Tiếng Anh</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>5A - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T19" s="10" t="inlineStr">
-        <is>
-          <t>1A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>3A - GDTC</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr"/>
+      <c r="T19" s="10" t="inlineStr"/>
       <c r="U19" s="10" t="inlineStr"/>
       <c r="V19" s="10" t="inlineStr"/>
     </row>
@@ -4056,47 +4056,47 @@
           <t>2A - Toán</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>2B - Toán</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>4A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Việt</t>
+          <t>5A - HĐTN</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O20" s="10" t="inlineStr"/>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>2B - TC Toán</t>
+        </is>
+      </c>
       <c r="P20" s="10" t="inlineStr"/>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>4B - Tiếng Anh</t>
+          <t>1B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr"/>
-      <c r="T20" s="10" t="inlineStr">
-        <is>
-          <t>4A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>3A - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T20" s="10" t="inlineStr"/>
       <c r="U20" s="10" t="inlineStr"/>
       <c r="V20" s="10" t="inlineStr"/>
     </row>
@@ -4109,26 +4109,22 @@
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H21" s="10" t="inlineStr"/>
       <c r="I21" s="10" t="inlineStr"/>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>4A - Toán</t>
+          <t>4A - Tiếng Việt</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
@@ -4140,28 +4136,32 @@
       <c r="M21" s="10" t="inlineStr"/>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>1B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="inlineStr"/>
+          <t>1A - Đạo đức</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>3A - TC Toán</t>
+        </is>
+      </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>5A - LS &amp; ĐL</t>
+          <t>5B - Công nghệ</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
+          <t>2B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R21" s="10" t="inlineStr"/>
       <c r="S21" s="10" t="inlineStr"/>
-      <c r="T21" s="10" t="inlineStr">
-        <is>
-          <t>3A - Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="U21" s="10" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr"/>
+      <c r="U21" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tin học</t>
+        </is>
+      </c>
       <c r="V21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4174,29 +4174,37 @@
       </c>
       <c r="D22" s="10" t="inlineStr"/>
       <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>3A - TTCM</t>
+          <t>3A - Toán</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr"/>
+          <t>4A - Đạo đức</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M22" s="10" t="inlineStr"/>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>1B - Đạo đức</t>
+          <t>1A - TC Toán</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -4204,28 +4212,20 @@
           <t>2A - TC Tiếng Việt</t>
         </is>
       </c>
-      <c r="P22" s="10" t="inlineStr"/>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>4B - Khoa học</t>
+        </is>
+      </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Anh</t>
+          <t>5B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>1A - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T22" s="10" t="inlineStr">
-        <is>
-          <t>2B - Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="U22" s="10" t="inlineStr">
-        <is>
-          <t>5B - Tin học</t>
-        </is>
-      </c>
+      <c r="S22" s="10" t="inlineStr"/>
+      <c r="T22" s="10" t="inlineStr"/>
+      <c r="U22" s="10" t="inlineStr"/>
       <c r="V22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
@@ -4243,56 +4243,56 @@
       <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>1A - Toán</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr"/>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr">
         <is>
           <t>2B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>3A - Toán</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>4A - Toán</t>
+        </is>
+      </c>
       <c r="K23" s="10" t="inlineStr"/>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>5A - TC Tiếng Việt</t>
+          <t>5A - Tiếng Việt</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Việt</t>
+          <t>5B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="10" t="inlineStr">
-        <is>
-          <t>4B - Khoa học</t>
-        </is>
-      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>2A - TC Toán</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr"/>
       <c r="Q23" s="10" t="inlineStr">
         <is>
-          <t>1B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>4A - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T23" s="10" t="inlineStr">
-        <is>
-          <t>2A - Mỹ thuật</t>
-        </is>
-      </c>
+          <t>3A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>4B - GDTC</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr"/>
+      <c r="T23" s="10" t="inlineStr"/>
       <c r="U23" s="10" t="inlineStr"/>
       <c r="V23" s="10" t="inlineStr"/>
     </row>
@@ -4304,31 +4304,31 @@
           <t>Tiết 6</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>2B - GDTC</t>
+        </is>
+      </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
           <t>1A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
       <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>4B - HĐTN</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
+      <c r="K24" s="10" t="inlineStr"/>
+      <c r="L24" s="10" t="inlineStr"/>
       <c r="M24" s="10" t="inlineStr">
         <is>
           <t>5B - Tiếng Việt</t>
@@ -4336,26 +4336,26 @@
       </c>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>2A - Đạo đức</t>
+          <t>1B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O24" s="10" t="inlineStr"/>
       <c r="P24" s="10" t="inlineStr">
         <is>
-          <t>4A - LS &amp; ĐL</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Anh</t>
-        </is>
-      </c>
+          <t>5A - LS &amp; ĐL</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr"/>
       <c r="R24" s="10" t="inlineStr">
         <is>
-          <t>3A - GDTC</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr"/>
+          <t>4A - GDTC</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>4B - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T24" s="10" t="inlineStr"/>
       <c r="U24" s="10" t="inlineStr"/>
       <c r="V24" s="10" t="inlineStr"/>
@@ -4372,55 +4372,55 @@
       <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>1B - HĐTN</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>1B - Toán</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>3A - TC Toán</t>
+          <t>3A - Tiếng Việt</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>4B - Đạo đức</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr"/>
+          <t>4A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>1A - GDTC</t>
+          <t>2A - Đạo đức</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Toán</t>
+          <t>2B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>5B - LS &amp; ĐL</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr"/>
+          <t>4B - LS &amp; ĐL</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Anh</t>
+        </is>
+      </c>
       <c r="R25" s="10" t="inlineStr"/>
       <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
+      <c r="T25" s="10" t="inlineStr">
+        <is>
+          <t>1A - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U25" s="10" t="inlineStr"/>
       <c r="V25" s="10" t="inlineStr"/>
     </row>
@@ -4443,29 +4443,25 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>1A - Toán</t>
+          <t>1A - Tiếng Việt</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
-      <c r="G26" s="13" t="inlineStr"/>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>2B - HĐTN</t>
-        </is>
-      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr"/>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>3A - TTCM</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>4B - Toán</t>
+          <t>4B - Tiếng Việt</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -4473,7 +4469,11 @@
           <t>5A - Toán</t>
         </is>
       </c>
-      <c r="M26" s="13" t="inlineStr"/>
+      <c r="M26" s="13" t="inlineStr">
+        <is>
+          <t>5B - HĐTN</t>
+        </is>
+      </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
           <t>1B - GDTC</t>
@@ -4481,13 +4481,13 @@
       </c>
       <c r="O26" s="13" t="inlineStr">
         <is>
-          <t>2A - TC Tiếng Việt</t>
+          <t>2B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="P26" s="13" t="inlineStr"/>
       <c r="Q26" s="13" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
+          <t>4A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R26" s="13" t="inlineStr"/>
@@ -4505,53 +4505,53 @@
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr"/>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr"/>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>2B - Toán</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>4A - TC Toán</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>5A - HĐTN</t>
-        </is>
-      </c>
-      <c r="M27" s="13" t="inlineStr"/>
+          <t>4A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>1B - TC Toán</t>
-        </is>
-      </c>
-      <c r="O27" s="13" t="inlineStr"/>
+          <t>1A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>2A - TC Toán</t>
+        </is>
+      </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>5B - Khoa học</t>
+          <t>5A - Khoa học</t>
         </is>
       </c>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>4B - Tiếng Anh</t>
+          <t>3A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R27" s="13" t="inlineStr"/>
@@ -4571,55 +4571,55 @@
       <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr"/>
       <c r="F28" s="13" t="inlineStr"/>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>2B - Toán</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr"/>
+          <t>2B - HĐTN</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr"/>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>4B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L28" s="13" t="inlineStr"/>
+          <t>4B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>5B - Đạo đức</t>
+          <t>5B - Tiếng Việt</t>
         </is>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>1A - TC Toán</t>
-        </is>
-      </c>
-      <c r="O28" s="13" t="inlineStr"/>
+          <t>1A - GDTC</t>
+        </is>
+      </c>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>2A - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="P28" s="13" t="inlineStr">
         <is>
-          <t>5A - Khoa học</t>
+          <t>4A - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q28" s="13" t="inlineStr">
         <is>
-          <t>3A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R28" s="13" t="inlineStr">
-        <is>
-          <t>4A - GDTC</t>
-        </is>
-      </c>
-      <c r="S28" s="13" t="inlineStr">
-        <is>
-          <t>1B - Âm nhạc</t>
-        </is>
-      </c>
+          <t>1B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R28" s="13" t="inlineStr"/>
+      <c r="S28" s="13" t="inlineStr"/>
       <c r="T28" s="13" t="inlineStr"/>
       <c r="U28" s="13" t="inlineStr"/>
       <c r="V28" s="13" t="inlineStr"/>
@@ -4632,60 +4632,60 @@
           <t>Tiết 4</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2B - GDTC</t>
-        </is>
-      </c>
+      <c r="D29" s="13" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
         <is>
           <t>1A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>1B - Toán</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr"/>
+      <c r="F29" s="13" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="H29" s="13" t="inlineStr"/>
-      <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>3A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr"/>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr"/>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N29" s="13" t="inlineStr"/>
-      <c r="O29" s="13" t="inlineStr">
-        <is>
-          <t>3A - Công nghệ</t>
-        </is>
-      </c>
+          <t>4B - HĐTN</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr"/>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>1B - TC Toán</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="inlineStr"/>
       <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>2A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R29" s="13" t="inlineStr">
-        <is>
-          <t>5A - GDTC</t>
-        </is>
-      </c>
-      <c r="S29" s="13" t="inlineStr"/>
+          <t>5B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R29" s="13" t="inlineStr"/>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>2B - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T29" s="13" t="inlineStr"/>
-      <c r="U29" s="13" t="inlineStr"/>
+      <c r="U29" s="13" t="inlineStr">
+        <is>
+          <t>4A - Tin học</t>
+        </is>
+      </c>
       <c r="V29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
@@ -4712,14 +4712,22 @@
           <t>2A - Toán</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr"/>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>3A - Tiếng Việt</t>
+          <t>3A - Toán</t>
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr"/>
-      <c r="K30" s="13" t="inlineStr"/>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>4B - Toán</t>
+        </is>
+      </c>
       <c r="L30" s="13" t="inlineStr"/>
       <c r="M30" s="13" t="inlineStr">
         <is>
@@ -4731,16 +4739,8 @@
           <t>1A - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
-      <c r="O30" s="13" t="inlineStr">
-        <is>
-          <t>2B - Đạo đức</t>
-        </is>
-      </c>
-      <c r="P30" s="13" t="inlineStr">
-        <is>
-          <t>4B - Khoa học</t>
-        </is>
-      </c>
+      <c r="O30" s="13" t="inlineStr"/>
+      <c r="P30" s="13" t="inlineStr"/>
       <c r="Q30" s="13" t="inlineStr">
         <is>
           <t>5A - Tiếng Anh</t>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="R30" s="13" t="inlineStr"/>
       <c r="S30" s="13" t="inlineStr"/>
-      <c r="T30" s="13" t="inlineStr"/>
-      <c r="U30" s="13" t="inlineStr">
-        <is>
-          <t>4A - Tin học</t>
-        </is>
-      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t>4A - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr"/>
       <c r="V30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
@@ -4764,60 +4764,60 @@
           <t>Tiết 6</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>2A - GDTC</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr"/>
       <c r="F31" s="13" t="inlineStr"/>
       <c r="G31" s="13" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>3A - Toán</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr"/>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>4A - Toán</t>
+        </is>
+      </c>
       <c r="K31" s="13" t="inlineStr"/>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr">
-        <is>
-          <t>5B - TC Toán</t>
-        </is>
-      </c>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="13" t="inlineStr"/>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>1B - TC Toán</t>
+          <t>1B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>2A - TC Toán</t>
-        </is>
-      </c>
-      <c r="P31" s="13" t="inlineStr">
-        <is>
-          <t>4B - Công nghệ</t>
-        </is>
-      </c>
+          <t>2B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="inlineStr"/>
       <c r="Q31" s="13" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
+          <t>1A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R31" s="13" t="inlineStr"/>
-      <c r="S31" s="13" t="inlineStr"/>
-      <c r="T31" s="13" t="inlineStr"/>
-      <c r="U31" s="13" t="inlineStr"/>
+      <c r="S31" s="13" t="inlineStr">
+        <is>
+          <t>5A - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T31" s="13" t="inlineStr">
+        <is>
+          <t>4B - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U31" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tin học</t>
+        </is>
+      </c>
       <c r="V31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
@@ -4829,57 +4829,57 @@
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1B - Tiếng Việt</t>
+          <t>1B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr"/>
-      <c r="H32" s="13" t="inlineStr"/>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>3A - HĐTN</t>
+          <t>3A - TC Toán</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>4A - Toán</t>
+          <t>4A - Tiếng Việt</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr"/>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="L32" s="13" t="inlineStr"/>
+      <c r="M32" s="13" t="inlineStr"/>
       <c r="N32" s="13" t="inlineStr">
         <is>
-          <t>2B - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O32" s="13" t="inlineStr">
-        <is>
-          <t>2A - TC Toán</t>
-        </is>
-      </c>
-      <c r="P32" s="13" t="inlineStr"/>
+          <t>2A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O32" s="13" t="inlineStr"/>
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>5A - LS &amp; ĐL</t>
+        </is>
+      </c>
       <c r="Q32" s="13" t="inlineStr">
         <is>
-          <t>1A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R32" s="13" t="inlineStr"/>
-      <c r="S32" s="13" t="inlineStr">
-        <is>
-          <t>4B - Âm nhạc</t>
-        </is>
-      </c>
+          <t>4B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R32" s="13" t="inlineStr">
+        <is>
+          <t>5B - GDTC</t>
+        </is>
+      </c>
+      <c r="S32" s="13" t="inlineStr"/>
       <c r="T32" s="13" t="inlineStr"/>
       <c r="U32" s="13" t="inlineStr"/>
       <c r="V32" s="13" t="inlineStr"/>
@@ -4903,7 +4903,7 @@
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Việt</t>
+          <t>1A - HĐTN</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>2A - Toán</t>
+          <t>2A - Tiếng Việt</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -4923,23 +4923,19 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>3A - TTCM</t>
+          <t>3A - HĐTN</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>4A - TC Tiếng Việt</t>
+          <t>4A - Toán</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
+      <c r="L33" s="10" t="inlineStr"/>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Việt</t>
+          <t>5B - Toán</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr"/>
@@ -4952,7 +4948,11 @@
       </c>
       <c r="R33" s="10" t="inlineStr"/>
       <c r="S33" s="10" t="inlineStr"/>
-      <c r="T33" s="10" t="inlineStr"/>
+      <c r="T33" s="10" t="inlineStr">
+        <is>
+          <t>5A - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U33" s="10" t="inlineStr"/>
       <c r="V33" s="10" t="inlineStr"/>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>2A - Tiếng Việt</t>
+          <t>2A - Toán</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -4986,37 +4986,37 @@
           <t>3A - Toán</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
+      <c r="J34" s="10" t="inlineStr"/>
       <c r="K34" s="10" t="inlineStr">
         <is>
           <t>4B - Toán</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr"/>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>5A - Toán</t>
+        </is>
+      </c>
       <c r="M34" s="10" t="inlineStr"/>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>1A - TC Toán</t>
+          <t>1A - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="10" t="inlineStr">
-        <is>
-          <t>5B - LS &amp; ĐL</t>
-        </is>
-      </c>
+      <c r="P34" s="10" t="inlineStr"/>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Anh</t>
+          <t>4A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R34" s="10" t="inlineStr"/>
       <c r="S34" s="10" t="inlineStr"/>
-      <c r="T34" s="10" t="inlineStr"/>
+      <c r="T34" s="10" t="inlineStr">
+        <is>
+          <t>5B - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U34" s="10" t="inlineStr"/>
       <c r="V34" s="10" t="inlineStr"/>
     </row>
@@ -5029,12 +5029,12 @@
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>1A - Toán</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
@@ -5045,43 +5045,43 @@
           <t>2B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
           <t>4A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr"/>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>5B - Toán</t>
+          <t>5B - TC Toán</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>1A - TC Tiếng Việt</t>
+          <t>1B - GDTC</t>
         </is>
       </c>
       <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" s="10" t="inlineStr"/>
-      <c r="Q35" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Anh</t>
-        </is>
-      </c>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>5A - Công nghệ</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr"/>
       <c r="R35" s="10" t="inlineStr"/>
       <c r="S35" s="10" t="inlineStr"/>
       <c r="T35" s="10" t="inlineStr"/>
-      <c r="U35" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tin học</t>
-        </is>
-      </c>
+      <c r="U35" s="10" t="inlineStr"/>
       <c r="V35" s="10" t="inlineStr"/>
     </row>
     <row r="36">

--- a/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
+++ b/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
@@ -710,7 +710,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Tiếng Việt
 (Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
@@ -903,8 +903,8 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Đạo đức
+(Phượng)</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -921,8 +921,8 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
+          <t>Tiếng Việt
+(Chiên (GVCN 2B))</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -966,8 +966,8 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Âm nhạc
+(Tươi (Âm nhạc))</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -984,8 +984,8 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+          <t>TC Toán
+(Lập)</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -1100,8 +1100,8 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>HĐTN
+(Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1289,8 +1289,8 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Phượng)</t>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1482,8 +1482,8 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Phượng)</t>
+          <t>Tiếng Việt
+(Đỗ Hương (GVCN 1A))</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1500,8 +1500,8 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>TC Toán
-(Lập)</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -2069,8 +2069,8 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>TC Toán
+(Phượng)</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>TC Toán
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
@@ -3127,7 +3127,7 @@
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>1A - HĐTN</t>
+          <t>1A - Tiếng Việt</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -3321,11 +3321,7 @@
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E9" s="10" t="inlineStr"/>
       <c r="F9" s="10" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
@@ -3336,7 +3332,11 @@
           <t>2A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>3A - TC Toán</t>
@@ -3356,7 +3356,7 @@
       <c r="M9" s="10" t="inlineStr"/>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>2B - Tự nhiên &amp; Xã hội</t>
+          <t>1A - Đạo đức</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr"/>
@@ -3385,22 +3385,14 @@
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E10" s="10" t="inlineStr"/>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="10" t="inlineStr">
         <is>
           <t>3A - TTCM</t>
@@ -3427,7 +3419,11 @@
           <t>1B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
-      <c r="O10" s="10" t="inlineStr"/>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>2B - TC Toán</t>
+        </is>
+      </c>
       <c r="P10" s="10" t="inlineStr"/>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -3435,7 +3431,11 @@
         </is>
       </c>
       <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>1A - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T10" s="10" t="inlineStr"/>
       <c r="U10" s="10" t="inlineStr"/>
       <c r="V10" s="10" t="inlineStr"/>
@@ -3521,7 +3521,11 @@
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>1A - HĐTN</t>
+        </is>
+      </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
           <t>1B - Toán</t>
@@ -3567,11 +3571,7 @@
           <t>4B - GDTC</t>
         </is>
       </c>
-      <c r="S12" s="13" t="inlineStr">
-        <is>
-          <t>1A - Âm nhạc</t>
-        </is>
-      </c>
+      <c r="S12" s="13" t="inlineStr"/>
       <c r="T12" s="13" t="inlineStr"/>
       <c r="U12" s="13" t="inlineStr"/>
       <c r="V12" s="13" t="inlineStr"/>
@@ -3713,7 +3713,11 @@
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
@@ -3746,11 +3750,7 @@
       </c>
       <c r="L15" s="13" t="inlineStr"/>
       <c r="M15" s="13" t="inlineStr"/>
-      <c r="N15" s="13" t="inlineStr">
-        <is>
-          <t>1A - GDTC</t>
-        </is>
-      </c>
+      <c r="N15" s="13" t="inlineStr"/>
       <c r="O15" s="13" t="inlineStr"/>
       <c r="P15" s="13" t="inlineStr"/>
       <c r="Q15" s="13" t="inlineStr"/>
@@ -3909,7 +3909,11 @@
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F18" s="13" t="inlineStr"/>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -3936,14 +3940,10 @@
       <c r="M18" s="13" t="inlineStr"/>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>1A - Đạo đức</t>
-        </is>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
-        <is>
-          <t>2B - TC Toán</t>
-        </is>
-      </c>
+          <t>2B - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O18" s="13" t="inlineStr"/>
       <c r="P18" s="13" t="inlineStr"/>
       <c r="Q18" s="13" t="inlineStr">
         <is>
@@ -4505,11 +4505,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E27" s="13" t="inlineStr"/>
       <c r="F27" s="13" t="inlineStr"/>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4526,11 @@
           <t>5B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="N27" s="13" t="inlineStr"/>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>1A - TC Toán</t>
+        </is>
+      </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
           <t>3A - TC Toán</t>
@@ -4864,7 +4864,7 @@
       <c r="M32" s="13" t="inlineStr"/>
       <c r="N32" s="13" t="inlineStr">
         <is>
-          <t>1A - TC Toán</t>
+          <t>1A - GDTC</t>
         </is>
       </c>
       <c r="O32" s="13" t="inlineStr"/>

--- a/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
+++ b/Thoi_Khoa_Bieu_Truong_9_Lop.xlsx
@@ -532,15 +532,15 @@
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,56 +576,47 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 1A
-(Khối 1)</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 1B
-(Khối 1)</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 2A
-(Khối 2)</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 2B
-(Khối 2)</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 3A
-(Khối 3)</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 4A
-(Khối 4)</t>
+          <t>4A</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 4B
-(Khối 4)</t>
+          <t>4B</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 5A
-(Khối 5)</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Lớp 5B
-(Khối 5)</t>
+          <t>5B</t>
         </is>
       </c>
     </row>
@@ -648,55 +639,55 @@
       <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Chào cờ
-(BGH (Toàn trường))</t>
+(BGH)</t>
         </is>
       </c>
     </row>
@@ -711,55 +702,55 @@
       <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật)</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Đạo đức
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>LS &amp; ĐL
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -773,55 +764,55 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
+          <t>TC Toán
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
           <t>TC Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+(Lập)</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+(Nhiên)</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Toán
+(Lan)</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>Tiếng Việt
+(Nhật)</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Tiếng Việt
+(Thanh)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>LS &amp; ĐL
 (Hiền)</t>
         </is>
       </c>
@@ -837,55 +828,55 @@
       <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>HĐTN
-(Hà Hương (GVCN 1B))</t>
+          <t>Tiếng Việt
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
           <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Tin học
-(Nga (Tin học))</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+(Tấm)</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Nhật)</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Tiếng Việt
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Công nghệ
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -903,56 +894,56 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
 (Phượng)</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+          <t>TC Tiếng Việt
+(Lập)</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+          <t>GDTC
+(Hà)</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>TC Toán
-(Nhiên(GVCN 3A))</t>
+          <t>GDTC
+(Tấm)</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>LS &amp; ĐL
 (Hiền)</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -966,56 +957,56 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
+          <t>Đạo đức
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
           <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
 (Lập)</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>TTCM
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Lan (GVCN 4A))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>LS &amp; ĐL
+(Hiền)</t>
         </is>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
+          <t>GDTC
+(Tấm)</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Toán
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1029,127 +1020,127 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+(Việt)</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Công nghệ
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
+(Tấm)</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
+(Nõn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Tiết 1</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Toán
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>TC Tiếng Việt
 (Lập)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Khoa học
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga)</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật)</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>TC Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Thứ 3</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Tiết 1</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1163,56 +1154,56 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
+          <t>Âm nhạc
+(Tươi)</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Đạo đức
 (Phượng)</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+          <t>HĐTN
+(Chiên)</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>TTCM
-(Nhiên(GVCN 3A))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
+          <t>Toán
+(Lan)</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Đạo đức
-(Nhật (GVCN 4B))</t>
+          <t>Toán
+(Nhật)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Toán
+(Thanh)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>HĐTN
-(Vũ Hương (GVCN 5B))</t>
+          <t>GDTC
+(Tấm)</t>
         </is>
       </c>
     </row>
@@ -1226,56 +1217,56 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi)</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
           <t>GDTC
-(Hà)</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>Công nghệ
-(Hiền)</t>
+(Tấm)</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>TC Toán
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1289,56 +1280,56 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Âm nhạc
+(Tươi)</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Toán
-(Thúy (GVCN 2A))</t>
+(Thúy)</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Toán
-(Chiên (GVCN 2B))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+          <t>TC Toán
+(Lập)</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+          <t>HĐTN
+(Lan)</t>
         </is>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>Mỹ thuật
+(Việt)</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Tiếng Việt
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1356,14 +1347,14 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Phượng)</t>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Nõn)</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -1374,38 +1365,38 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+          <t>Toán
+(Nhiên)</t>
         </is>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>Tin học
-(Nga (Tin học))</t>
+          <t>Khoa học
+(Hiền)</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Tiếng Việt
+(Nhật)</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
+(Thanh)</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1419,56 +1410,56 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Phượng)</t>
+          <t>Tiếng Việt
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>HĐTN
-(Thúy (GVCN 2A))</t>
+          <t>Tiếng Việt
+(Thúy)</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
+          <t>Toán
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
           <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
+(Việt)</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
+          <t>LS &amp; ĐL
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Vũ Hương (GVCN 5B))</t>
+(Nõn)</t>
         </is>
       </c>
     </row>
@@ -1482,56 +1473,56 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>TC Tiếng Việt
+(Phượng)</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
+          <t>Toán
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
+(Hà)</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>Khoa học
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
           <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>HĐTN
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
+(Việt)</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>Toán
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1553,56 +1544,56 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
+          <t>TC Tiếng Việt
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
           <t>GDTC
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
+(Tấm)</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Công nghệ
 (Hiền)</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Đạo đức
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1616,56 +1607,56 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Toán
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>GDTC
-(Phượng)</t>
+          <t>Tiếng Việt
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+(Thúy)</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi)</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga)</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>Khoa học
 (Hiền)</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
         </is>
       </c>
     </row>
@@ -1679,56 +1670,56 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Toán
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+(Nõn)</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>GDTC
-(Hà)</t>
+          <t>Tiếng Việt
+(Chiên)</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
-(Lập)</t>
+          <t>Mỹ thuật
+(Việt)</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>Tiếng Việt
+(Lan)</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
+          <t>Công nghệ
 (Hiền)</t>
         </is>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>Tiếng Việt
+(Thanh)</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
+          <t>Tiếng Việt
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1742,56 +1733,56 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>TC Toán
-(Phượng)</t>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>Toán
+(Thúy)</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Công nghệ
-(Lập)</t>
+          <t>TC Tiếng Việt
+(Nhiên)</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>LS &amp; ĐL
+(Hiền)</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Khoa học
-(Hiền)</t>
+          <t>Âm nhạc
+(Tươi)</t>
         </is>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>HĐTN
-(Thanh (GVCN 5A))</t>
+          <t>Tiếng Việt
+(Thanh)</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1809,56 +1800,56 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+(Việt)</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>GDTC
+(Hà)</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
+(Nhật)</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Toán
-(Thanh (GVCN 5A))</t>
+          <t>Âm nhạc
+(Tươi)</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
+          <t>HĐTN
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -1872,14 +1863,14 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Tự nhiên &amp; Xã hội
+(Phượng)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1890,26 +1881,26 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
+          <t>Âm nhạc
+(Tươi)</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>TC Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+          <t>Tiếng Việt
+(Nhiên)</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+(Lan)</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>Tiếng Việt
+(Nhật)</t>
         </is>
       </c>
       <c r="K24" s="10" t="inlineStr">
@@ -1920,8 +1911,8 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
     </row>
@@ -1935,56 +1926,56 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>Đạo đức
+(Phượng)</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
+          <t>HĐTN
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+(Việt)</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Lập)</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+(Nhiên)</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
+          <t>Tin học
+(Nga)</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>LS &amp; ĐL
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2006,56 +1997,56 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>TC Toán
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>TTCM
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Đạo đức
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
           <t>Toán
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Tự nhiên &amp; Xã hội
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>Đạo đức
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
-        </is>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>Khoa học
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Thanh (GVCN 5A))</t>
+(Thanh)</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2069,56 +2060,56 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>TC Toán
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
 (Phượng)</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Toán
-(Thúy (GVCN 2A))</t>
+(Thúy)</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
           <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>Công nghệ
-(Hiền)</t>
+(Nhật)</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
+          <t>HĐTN
+(Thanh)</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+          <t>Toán
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2133,55 +2124,55 @@
       <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
+          <t>TC Tiếng Việt
+(Phượng)</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>HĐTN
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
           <t>Đạo đức
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
 (Lập)</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
+          <t>HĐTN
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>GDTC
+(Tấm)</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật)</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>GDTC
-(Tấm (GDTC))</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>Đạo đức
-(Vũ Hương (GVCN 5B))</t>
+(Nõn)</t>
         </is>
       </c>
     </row>
@@ -2196,55 +2187,55 @@
       <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>TC Toán
+(Phượng)</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Toán
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Công nghệ
+(Lập)</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
           <t>Đạo đức
-(Phượng)</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
+(Nhật)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>LS &amp; ĐL
-(Hiền)</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>Tin học
-(Nga (Tin học))</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
+(Nõn)</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
+          <t>Mỹ thuật
+(Việt)</t>
         </is>
       </c>
     </row>
@@ -2262,56 +2253,56 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Tự nhiên &amp; Xã hội
+          <t>TC Toán
 (Phượng)</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi)</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>TC Toán
 (Lập)</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
+(Nhiên)</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+          <t>Toán
+(Lan)</t>
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>TC Tiếng Việt
+(Nhật)</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>Khoa học
 (Hiền)</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga)</t>
         </is>
       </c>
     </row>
@@ -2332,49 +2323,49 @@
       <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+          <t>TC Tiếng Việt
+(Lập)</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+(Việt)</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
           <t>TC Toán
-(Lập)</t>
-        </is>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
+(Nhiên)</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
+(Lan)</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
+          <t>HĐTN
+(Nhật)</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-(Việt (Mỹ thuật))</t>
+          <t>LS &amp; ĐL
+(Hiền)</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>Âm nhạc
-(Tươi (Âm nhạc))</t>
+          <t>GDTC
+(Tấm)</t>
         </is>
       </c>
     </row>
@@ -2394,52 +2385,52 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+          <t>Toán
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+          <t>GDTC
+(Hà)</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>HĐTN
-(Chiên (GVCN 2B))</t>
+          <t>TC Tiếng Việt
+(Lập)</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>HĐTN
-(Nhiên(GVCN 3A))</t>
+          <t>Toán
+(Nhiên)</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>Toán
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
         <is>
           <t>Khoa học
 (Hiền)</t>
         </is>
       </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Nhật)</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Tin học
+(Nga)</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+(Tươi)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2459,56 +2450,56 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+          <t>HĐTN
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+          <t>Tiếng Anh
+(Nõn)</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>TC Tiếng Việt
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Lan)</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Lan (GVCN 4A))</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>TC Tiếng Việt
-(Nhật (GVCN 4B))</t>
+(Nhật)</t>
         </is>
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
+          <t>Đạo đức
+(Thanh)</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Thanh (GVCN 5A))</t>
-        </is>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2523,55 +2514,55 @@
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
+          <t>Toán
+(Thúy)</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
+(Chiên)</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>TTCM
-(Nhiên(GVCN 3A))</t>
+          <t>Tiếng Việt
+(Nhiên)</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Lan (GVCN 4A))</t>
+(Lan)</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-(Nhật (GVCN 4B))</t>
+          <t>TC Toán
+(Nhật)</t>
         </is>
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
           <t>Tiếng Anh
-(Nõn (Anh))</t>
+(Nõn)</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr">
         <is>
-          <t>Toán
-(Vũ Hương (GVCN 5B))</t>
+          <t>Khoa học
+(Hiền)</t>
         </is>
       </c>
     </row>
@@ -2585,56 +2576,56 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+(Đỗ Hương)</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Hà Hương)</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Thúy)</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+(Chiên)</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
           <t>Toán
-(Đỗ Hương (GVCN 1A))</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
+(Nhiên)</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+(Nõn)</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>Khoa học
+(Hiền)</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>Toán
-(Hà Hương (GVCN 1B))</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Thúy (GVCN 2A))</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-(Chiên (GVCN 2B))</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhiên(GVCN 3A))</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-(Nõn (Anh))</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>Toán
-(Nhật (GVCN 4B))</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>Đạo đức
-(Thanh (GVCN 5A))</t>
+(Thanh)</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
           <t>Tiếng Việt
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2649,55 +2640,55 @@
       <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Đỗ Hương (GVCN 1A))</t>
+(Đỗ Hương)</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Hà Hương (GVCN 1B))</t>
+(Hà Hương)</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Thúy (GVCN 2A))</t>
+(Thúy)</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Chiên (GVCN 2B))</t>
+(Chiên)</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Nhiên(GVCN 3A))</t>
+(Nhiên)</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Lan (GVCN 4A))</t>
+(Lan)</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Nhật (GVCN 4B))</t>
+(Nhật)</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Thanh (GVCN 5A))</t>
+(Thanh)</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
           <t>Sinh hoạt lớp
-(Vũ Hương (GVCN 5B))</t>
+(Vũ Hương)</t>
         </is>
       </c>
     </row>
@@ -2916,10 +2907,10 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2955,116 +2946,97 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Hà
-(PHT)</t>
+          <t>Hà</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Đỗ Hương (GVCN 1A)
-(GV_1A)</t>
+          <t>Đỗ Hương</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Hà Hương (GVCN 1B)
-(GV_1B)</t>
+          <t>Hà Hương</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Thúy (GVCN 2A)
-(GV_2A)</t>
+          <t>Thúy</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Chiên (GVCN 2B)
-(GV_2B)</t>
+          <t>Chiên</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Nhiên(GVCN 3A)
-(GV_3A)</t>
+          <t>Nhiên</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Lan (GVCN 4A)
-(GV_4A)</t>
+          <t>Lan</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Nhật (GVCN 4B)
-(GV_4B)</t>
+          <t>Nhật</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Thanh (GVCN 5A)
-(GV_5A)</t>
+          <t>Thanh</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Vũ Hương (GVCN 5B)
-(GV_5B)</t>
+          <t>Vũ Hương</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Phượng
-(GV_12)</t>
+          <t>Phượng</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Lập
-(GV_23)</t>
+          <t>Lập</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>Hiền
-(GV_45)</t>
+          <t>Hiền</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Nõn (Anh)
-(GV_ANH)</t>
+          <t>Nõn</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>Tấm (GDTC)
-(GV_TD)</t>
+          <t>Tấm</t>
         </is>
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>Tươi (Âm nhạc)
-(GV_NHAC)</t>
+          <t>Tươi</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>Việt (Mỹ thuật)
-(GV_HOA)</t>
+          <t>Việt</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>Nga (Tin học)
-(GV_TIN)</t>
+          <t>Nga</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>BGH (Toàn trường)
-(GV_CHUNG)</t>
+          <t>BGH</t>
         </is>
       </c>
     </row>
@@ -3130,15 +3102,15 @@
           <t>1A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>1B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>2B - Toán</t>
+          <t>2B - Tiếng Việt</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -3148,34 +3120,34 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>4A - Đạo đức</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr"/>
+          <t>4A - TC Toán</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L6" s="10" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>5B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="M6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
       <c r="O6" s="10" t="inlineStr"/>
       <c r="P6" s="10" t="inlineStr">
         <is>
-          <t>5A - LS &amp; ĐL</t>
+          <t>5B - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>2A - Tiếng Anh</t>
+          <t>5A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>4B - Âm nhạc</t>
-        </is>
-      </c>
+      <c r="S6" s="10" t="inlineStr"/>
       <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="10" t="inlineStr"/>
       <c r="V6" s="10" t="inlineStr"/>
@@ -3188,59 +3160,59 @@
           <t>Tiết 3</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>2A - GDTC</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>1A - TC Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
       <c r="F7" s="10" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H7" s="10" t="inlineStr"/>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>3A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr"/>
-      <c r="L7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>4A - Toán</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr"/>
-      <c r="O7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>1A - TC Toán</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>2B - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>5B - Công nghệ</t>
+          <t>5B - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R7" s="10" t="inlineStr">
-        <is>
-          <t>4B - GDTC</t>
-        </is>
-      </c>
+          <t>2A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr"/>
       <c r="S7" s="10" t="inlineStr"/>
-      <c r="T7" s="10" t="inlineStr">
-        <is>
-          <t>4A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="T7" s="10" t="inlineStr"/>
       <c r="U7" s="10" t="inlineStr"/>
       <c r="V7" s="10" t="inlineStr"/>
     </row>
@@ -3252,11 +3224,7 @@
           <t>Tiết 4</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>2B - GDTC</t>
-        </is>
-      </c>
+      <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="10" t="inlineStr">
         <is>
           <t>1A - Tiếng Việt</t>
@@ -3264,48 +3232,52 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>1B - HĐTN</t>
+          <t>1B - Tiếng Việt</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr"/>
-      <c r="L8" s="10" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>3A - Toán</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>4B - Toán</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>2A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
       <c r="O8" s="10" t="inlineStr"/>
       <c r="P8" s="10" t="inlineStr">
         <is>
-          <t>5A - Khoa học</t>
+          <t>5B - Công nghệ</t>
         </is>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
-          <t>4B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>2A - Âm nhạc</t>
-        </is>
-      </c>
+          <t>2B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>4A - GDTC</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr"/>
       <c r="T8" s="10" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tin học</t>
-        </is>
-      </c>
+      <c r="U8" s="10" t="inlineStr"/>
       <c r="V8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3320,57 +3292,57 @@
           <t>Tiết 5</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>3A - TC Toán</t>
-        </is>
-      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>2B - GDTC</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>1A - Toán</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>4B - HĐTN</t>
-        </is>
-      </c>
+      <c r="K9" s="10" t="inlineStr"/>
       <c r="L9" s="10" t="inlineStr">
         <is>
           <t>5A - Toán</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>1A - Đạo đức</t>
-        </is>
-      </c>
-      <c r="O9" s="10" t="inlineStr"/>
+          <t>1B - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>2A - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>5B - LS &amp; ĐL</t>
+          <t>4A - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R9" s="10" t="inlineStr"/>
+          <t>4B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>3A - GDTC</t>
+        </is>
+      </c>
       <c r="S9" s="10" t="inlineStr"/>
       <c r="T9" s="10" t="inlineStr"/>
       <c r="U9" s="10" t="inlineStr"/>
@@ -3385,57 +3357,57 @@
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F10" s="10" t="inlineStr"/>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>3A - TTCM</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>4A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M10" s="10" t="inlineStr"/>
+          <t>2A - Toán</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="inlineStr"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>1B - Tự nhiên &amp; Xã hội</t>
+          <t>1B - Đạo đức</t>
         </is>
       </c>
       <c r="O10" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Toán</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="inlineStr"/>
+          <t>3A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>4B - LS &amp; ĐL</t>
+        </is>
+      </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>1A - Âm nhạc</t>
-        </is>
-      </c>
+          <t>4A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>5A - GDTC</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr"/>
       <c r="T10" s="10" t="inlineStr"/>
       <c r="U10" s="10" t="inlineStr"/>
       <c r="V10" s="10" t="inlineStr"/>
@@ -3453,54 +3425,54 @@
       <c r="F11" s="10" t="inlineStr"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>2A - Toán</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>3A - Toán</t>
-        </is>
-      </c>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>2B - Toán</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
       <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>4B - Toán</t>
-        </is>
-      </c>
+      <c r="K11" s="10" t="inlineStr"/>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>5A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
+          <t>5A - TC Toán</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr"/>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>1B - TC Toán</t>
+          <t>1B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Tiếng Việt</t>
+          <t>3A - TC Toán</t>
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>4A - Khoa học</t>
+          <t>4A - Công nghệ</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R11" s="10" t="inlineStr"/>
+          <t>5B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>4B - GDTC</t>
+        </is>
+      </c>
       <c r="S11" s="10" t="inlineStr"/>
-      <c r="T11" s="10" t="inlineStr"/>
+      <c r="T11" s="10" t="inlineStr">
+        <is>
+          <t>1A - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U11" s="10" t="inlineStr"/>
       <c r="V11" s="10" t="inlineStr"/>
     </row>
@@ -3523,57 +3495,57 @@
       <c r="D12" s="13" t="inlineStr"/>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>1A - HĐTN</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>1B - Toán</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>1A - Toán</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>4A - TC Toán</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr"/>
+          <t>4A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>5B - Toán</t>
+          <t>5B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>2A - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O12" s="13" t="inlineStr"/>
-      <c r="P12" s="13" t="inlineStr">
-        <is>
-          <t>5A - LS &amp; ĐL</t>
-        </is>
-      </c>
+          <t>1B - GDTC</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>2B - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="P12" s="13" t="inlineStr"/>
       <c r="Q12" s="13" t="inlineStr"/>
-      <c r="R12" s="13" t="inlineStr">
-        <is>
-          <t>4B - GDTC</t>
-        </is>
-      </c>
+      <c r="R12" s="13" t="inlineStr"/>
       <c r="S12" s="13" t="inlineStr"/>
       <c r="T12" s="13" t="inlineStr"/>
-      <c r="U12" s="13" t="inlineStr"/>
+      <c r="U12" s="13" t="inlineStr">
+        <is>
+          <t>3A - Tin học</t>
+        </is>
+      </c>
       <c r="V12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
@@ -3585,59 +3557,59 @@
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="G13" s="13" t="inlineStr"/>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>3A - TTCM</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr"/>
+          <t>2B - HĐTN</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>4A - Toán</t>
+        </is>
+      </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>4B - Đạo đức</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr"/>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>5B - HĐTN</t>
-        </is>
-      </c>
+          <t>4B - Toán</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>5A - Toán</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr"/>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>1B - TC Tiếng Việt</t>
+          <t>2A - Đạo đức</t>
         </is>
       </c>
       <c r="O13" s="13" t="inlineStr"/>
-      <c r="P13" s="13" t="inlineStr">
-        <is>
-          <t>4A - LS &amp; ĐL</t>
-        </is>
-      </c>
-      <c r="Q13" s="13" t="inlineStr"/>
-      <c r="R13" s="13" t="inlineStr"/>
-      <c r="S13" s="13" t="inlineStr"/>
-      <c r="T13" s="13" t="inlineStr">
-        <is>
-          <t>1A - Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="U13" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tin học</t>
-        </is>
-      </c>
+      <c r="P13" s="13" t="inlineStr"/>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>3A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>5B - GDTC</t>
+        </is>
+      </c>
+      <c r="S13" s="13" t="inlineStr">
+        <is>
+          <t>1B - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T13" s="13" t="inlineStr"/>
+      <c r="U13" s="13" t="inlineStr"/>
       <c r="V13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -3648,11 +3620,7 @@
           <t>Tiết 3</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>2A - GDTC</t>
-        </is>
-      </c>
+      <c r="D14" s="13" t="inlineStr"/>
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr">
         <is>
@@ -3660,46 +3628,50 @@
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr"/>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>3A - Toán</t>
-        </is>
-      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="13" t="inlineStr">
         <is>
           <t>4A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>4B - Toán</t>
-        </is>
-      </c>
+      <c r="K14" s="13" t="inlineStr"/>
       <c r="L14" s="13" t="inlineStr"/>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>5B - TC Toán</t>
+        </is>
+      </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>1A - Tự nhiên &amp; Xã hội</t>
+          <t>1A - GDTC</t>
         </is>
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>2B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P14" s="13" t="inlineStr">
-        <is>
-          <t>5A - Công nghệ</t>
-        </is>
-      </c>
-      <c r="Q14" s="13" t="inlineStr"/>
+          <t>2A - TC Toán</t>
+        </is>
+      </c>
+      <c r="P14" s="13" t="inlineStr"/>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Anh</t>
+        </is>
+      </c>
       <c r="R14" s="13" t="inlineStr">
         <is>
-          <t>5B - GDTC</t>
-        </is>
-      </c>
-      <c r="S14" s="13" t="inlineStr"/>
+          <t>5A - GDTC</t>
+        </is>
+      </c>
+      <c r="S14" s="13" t="inlineStr">
+        <is>
+          <t>3A - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T14" s="13" t="inlineStr"/>
       <c r="U14" s="13" t="inlineStr"/>
       <c r="V14" s="13" t="inlineStr"/>
@@ -3713,11 +3685,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E15" s="13" t="inlineStr"/>
       <c r="F15" s="13" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
@@ -3728,44 +3696,48 @@
           <t>2A - Toán</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>2B - Toán</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>4A - HĐTN</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr"/>
       <c r="L15" s="13" t="inlineStr"/>
-      <c r="M15" s="13" t="inlineStr"/>
-      <c r="N15" s="13" t="inlineStr"/>
-      <c r="O15" s="13" t="inlineStr"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>3A - TC Toán</t>
+        </is>
+      </c>
       <c r="P15" s="13" t="inlineStr"/>
-      <c r="Q15" s="13" t="inlineStr"/>
-      <c r="R15" s="13" t="inlineStr">
-        <is>
-          <t>5A - GDTC</t>
-        </is>
-      </c>
-      <c r="S15" s="13" t="inlineStr"/>
-      <c r="T15" s="13" t="inlineStr"/>
-      <c r="U15" s="13" t="inlineStr">
-        <is>
-          <t>5B - Tin học</t>
-        </is>
-      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr"/>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>1A - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T15" s="13" t="inlineStr">
+        <is>
+          <t>4B - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U15" s="13" t="inlineStr"/>
       <c r="V15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
@@ -3781,17 +3753,25 @@
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="13" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>3A - TC Tiếng Việt</t>
+          <t>3A - Toán</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
           <t>5A - Tiếng Việt</t>
@@ -3804,7 +3784,7 @@
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
-          <t>1A - TC Tiếng Việt</t>
+          <t>2B - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O16" s="13" t="inlineStr">
@@ -3812,28 +3792,20 @@
           <t>2A - TC Tiếng Việt</t>
         </is>
       </c>
-      <c r="P16" s="13" t="inlineStr"/>
+      <c r="P16" s="13" t="inlineStr">
+        <is>
+          <t>4A - Khoa học</t>
+        </is>
+      </c>
       <c r="Q16" s="13" t="inlineStr">
         <is>
           <t>1B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R16" s="13" t="inlineStr"/>
-      <c r="S16" s="13" t="inlineStr">
-        <is>
-          <t>2B - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T16" s="13" t="inlineStr">
-        <is>
-          <t>4B - Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="U16" s="13" t="inlineStr">
-        <is>
-          <t>4A - Tin học</t>
-        </is>
-      </c>
+      <c r="S16" s="13" t="inlineStr"/>
+      <c r="T16" s="13" t="inlineStr"/>
+      <c r="U16" s="13" t="inlineStr"/>
       <c r="V16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3845,56 +3817,56 @@
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr"/>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr"/>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>2A - HĐTN</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr"/>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>2B - Toán</t>
+        </is>
+      </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>3A - TC Toán</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr"/>
       <c r="K17" s="13" t="inlineStr"/>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="inlineStr">
-        <is>
-          <t>5B - TC Toán</t>
-        </is>
-      </c>
+          <t>5A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>1B - GDTC</t>
+          <t>1A - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O17" s="13" t="inlineStr"/>
-      <c r="P17" s="13" t="inlineStr"/>
+      <c r="P17" s="13" t="inlineStr">
+        <is>
+          <t>4B - LS &amp; ĐL</t>
+        </is>
+      </c>
       <c r="Q17" s="13" t="inlineStr">
         <is>
-          <t>4B - Tiếng Anh</t>
+          <t>5B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R17" s="13" t="inlineStr"/>
       <c r="S17" s="13" t="inlineStr"/>
       <c r="T17" s="13" t="inlineStr">
         <is>
-          <t>2B - Mỹ thuật</t>
+          <t>4A - Mỹ thuật</t>
         </is>
       </c>
       <c r="U17" s="13" t="inlineStr"/>
@@ -3908,57 +3880,57 @@
           <t>Tiết 7</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>4A - HĐTN</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2A - GDTC</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr"/>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>1B - Toán</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>3A - TC Toán</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="13" t="inlineStr"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>2B - Tự nhiên &amp; Xã hội</t>
+          <t>1A - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="O18" s="13" t="inlineStr"/>
-      <c r="P18" s="13" t="inlineStr"/>
+      <c r="P18" s="13" t="inlineStr">
+        <is>
+          <t>4B - Khoa học</t>
+        </is>
+      </c>
       <c r="Q18" s="13" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R18" s="13" t="inlineStr">
-        <is>
-          <t>3A - GDTC</t>
-        </is>
-      </c>
+          <t>4A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr"/>
       <c r="S18" s="13" t="inlineStr"/>
       <c r="T18" s="13" t="inlineStr">
         <is>
-          <t>1B - Mỹ thuật</t>
+          <t>5A - Mỹ thuật</t>
         </is>
       </c>
       <c r="U18" s="13" t="inlineStr"/>
@@ -3981,58 +3953,58 @@
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>1A - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>1B - Tiếng Việt</t>
+          <t>1B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>2A - Toán</t>
+          <t>2A - Tiếng Việt</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr"/>
+          <t>2B - Toán</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
       <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>1A - GDTC</t>
-        </is>
-      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>5B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" s="10" t="inlineStr"/>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>4A - Công nghệ</t>
+          <t>5A - Công nghệ</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>3A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="inlineStr"/>
+          <t>4A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>4B - GDTC</t>
+        </is>
+      </c>
       <c r="S19" s="10" t="inlineStr"/>
-      <c r="T19" s="10" t="inlineStr">
-        <is>
-          <t>5B - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="T19" s="10" t="inlineStr"/>
       <c r="U19" s="10" t="inlineStr"/>
       <c r="V19" s="10" t="inlineStr"/>
     </row>
@@ -4047,10 +4019,14 @@
       <c r="D20" s="10" t="inlineStr"/>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr"/>
+          <t>1A - Toán</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>1B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
           <t>2A - Tiếng Việt</t>
@@ -4058,46 +4034,42 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>2B - Toán</t>
+          <t>2B - Tiếng Việt</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
       <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>5B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>1B - GDTC</t>
-        </is>
-      </c>
+      <c r="K20" s="10" t="inlineStr"/>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>5A - Toán</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" s="10" t="inlineStr"/>
       <c r="P20" s="10" t="inlineStr">
         <is>
-          <t>4A - Khoa học</t>
+          <t>5B - Khoa học</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>5A - Tiếng Anh</t>
+          <t>3A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R20" s="10" t="inlineStr"/>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>3A - Âm nhạc</t>
+          <t>4A - Âm nhạc</t>
         </is>
       </c>
       <c r="T20" s="10" t="inlineStr"/>
-      <c r="U20" s="10" t="inlineStr"/>
+      <c r="U20" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tin học</t>
+        </is>
+      </c>
       <c r="V20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4108,59 +4080,59 @@
           <t>Tiết 3</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>2B - GDTC</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr"/>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>1B - Toán</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>4A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr">
-        <is>
-          <t>1B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>3A - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
+          <t>5B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="10" t="inlineStr"/>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>4B - LS &amp; ĐL</t>
+          <t>4B - Công nghệ</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>4A - GDTC</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>5A - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T21" s="10" t="inlineStr"/>
+          <t>2A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr"/>
+      <c r="S21" s="10" t="inlineStr"/>
+      <c r="T21" s="10" t="inlineStr">
+        <is>
+          <t>3A - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U21" s="10" t="inlineStr"/>
       <c r="V21" s="10" t="inlineStr"/>
     </row>
@@ -4173,24 +4145,32 @@
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>1A - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>2A - Toán</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>3A - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="J22" s="10" t="inlineStr"/>
       <c r="K22" s="10" t="inlineStr"/>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>5A - HĐTN</t>
+          <t>5A - Tiếng Việt</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
@@ -4198,33 +4178,25 @@
           <t>5B - Tiếng Việt</t>
         </is>
       </c>
-      <c r="N22" s="10" t="inlineStr">
-        <is>
-          <t>1A - TC Toán</t>
-        </is>
-      </c>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>3A - Công nghệ</t>
-        </is>
-      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" s="10" t="inlineStr"/>
       <c r="P22" s="10" t="inlineStr">
         <is>
-          <t>4B - Khoa học</t>
+          <t>4A - LS &amp; ĐL</t>
         </is>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
+          <t>2B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
-      <c r="T22" s="10" t="inlineStr">
-        <is>
-          <t>2A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>4B - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T22" s="10" t="inlineStr"/>
       <c r="U22" s="10" t="inlineStr"/>
       <c r="V22" s="10" t="inlineStr"/>
     </row>
@@ -4240,23 +4212,23 @@
           <t>Tiết 5</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>1A - Toán</t>
-        </is>
-      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2B - GDTC</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr"/>
       <c r="F23" s="10" t="inlineStr"/>
       <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="10" t="inlineStr"/>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>3A - Toán</t>
+          <t>3A - Tiếng Việt</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>4A - Tiếng Việt</t>
+          <t>4A - Toán</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
@@ -4264,35 +4236,35 @@
           <t>4B - Toán</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>5B - HĐTN</t>
+        </is>
+      </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>1B - TC Toán</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
-        <is>
-          <t>2A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P23" s="10" t="inlineStr">
-        <is>
-          <t>5B - LS &amp; ĐL</t>
-        </is>
-      </c>
+          <t>2A - Tự nhiên &amp; Xã hội</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr"/>
+      <c r="P23" s="10" t="inlineStr"/>
       <c r="Q23" s="10" t="inlineStr">
         <is>
-          <t>2B - Tiếng Anh</t>
+          <t>1A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
-      <c r="T23" s="10" t="inlineStr"/>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>5A - Âm nhạc</t>
+        </is>
+      </c>
+      <c r="T23" s="10" t="inlineStr">
+        <is>
+          <t>1B - Mỹ thuật</t>
+        </is>
+      </c>
       <c r="U23" s="10" t="inlineStr"/>
       <c r="V23" s="10" t="inlineStr"/>
     </row>
@@ -4305,11 +4277,7 @@
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E24" s="10" t="inlineStr"/>
       <c r="F24" s="10" t="inlineStr">
         <is>
           <t>1B - Tiếng Việt</t>
@@ -4319,7 +4287,7 @@
       <c r="H24" s="10" t="inlineStr"/>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>3A - TC Tiếng Việt</t>
+          <t>3A - Tiếng Việt</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -4327,12 +4295,16 @@
           <t>4A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L24" s="10" t="inlineStr"/>
       <c r="M24" s="10" t="inlineStr"/>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>2B - Tự nhiên &amp; Xã hội</t>
+          <t>1A - Tự nhiên &amp; Xã hội</t>
         </is>
       </c>
       <c r="O24" s="10" t="inlineStr">
@@ -4347,15 +4319,15 @@
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
-          <t>4B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R24" s="10" t="inlineStr">
-        <is>
-          <t>5B - GDTC</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr"/>
+          <t>5B - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="inlineStr"/>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>2B - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T24" s="10" t="inlineStr"/>
       <c r="U24" s="10" t="inlineStr"/>
       <c r="V24" s="10" t="inlineStr"/>
@@ -4369,59 +4341,59 @@
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="E25" s="10" t="inlineStr"/>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>1B - Toán</t>
+          <t>1B - HĐTN</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="10" t="inlineStr"/>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>3A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>4B - TC Toán</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr"/>
+          <t>3A - Toán</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>2A - Tự nhiên &amp; Xã hội</t>
+          <t>1A - Đạo đức</t>
         </is>
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>2B - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr"/>
+          <t>2B - TC Toán</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>5A - LS &amp; ĐL</t>
+        </is>
+      </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
+          <t>4B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R25" s="10" t="inlineStr"/>
       <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
-      <c r="U25" s="10" t="inlineStr"/>
+      <c r="T25" s="10" t="inlineStr">
+        <is>
+          <t>2A - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>4A - Tin học</t>
+        </is>
+      </c>
       <c r="V25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4443,7 +4415,7 @@
       <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>1A - Toán</t>
+          <t>1A - Tiếng Việt</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr"/>
@@ -4452,13 +4424,25 @@
           <t>2A - Tiếng Việt</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr"/>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>3A - TTCM</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>4A - Đạo đức</t>
+        </is>
+      </c>
       <c r="K26" s="13" t="inlineStr"/>
       <c r="L26" s="13" t="inlineStr">
         <is>
-          <t>5A - TC Toán</t>
+          <t>5A - Toán</t>
         </is>
       </c>
       <c r="M26" s="13" t="inlineStr">
@@ -4468,31 +4452,19 @@
       </c>
       <c r="N26" s="13" t="inlineStr">
         <is>
-          <t>1B - Tự nhiên &amp; Xã hội</t>
-        </is>
-      </c>
-      <c r="O26" s="13" t="inlineStr">
-        <is>
-          <t>2B - Đạo đức</t>
-        </is>
-      </c>
-      <c r="P26" s="13" t="inlineStr">
-        <is>
-          <t>4B - Khoa học</t>
-        </is>
-      </c>
+          <t>1B - TC Toán</t>
+        </is>
+      </c>
+      <c r="O26" s="13" t="inlineStr"/>
+      <c r="P26" s="13" t="inlineStr"/>
       <c r="Q26" s="13" t="inlineStr">
         <is>
-          <t>4A - Tiếng Anh</t>
+          <t>4B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R26" s="13" t="inlineStr"/>
       <c r="S26" s="13" t="inlineStr"/>
-      <c r="T26" s="13" t="inlineStr">
-        <is>
-          <t>3A - Mỹ thuật</t>
-        </is>
-      </c>
+      <c r="T26" s="13" t="inlineStr"/>
       <c r="U26" s="13" t="inlineStr"/>
       <c r="V26" s="13" t="inlineStr"/>
     </row>
@@ -4514,48 +4486,48 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>2B - Toán</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr"/>
-      <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
+          <t>2B - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>3A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>4A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>4B - Toán</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>5A - HĐTN</t>
+        </is>
+      </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>5B - Tiếng Việt</t>
+          <t>5B - Toán</t>
         </is>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>1A - TC Toán</t>
-        </is>
-      </c>
-      <c r="O27" s="13" t="inlineStr">
-        <is>
-          <t>3A - TC Toán</t>
-        </is>
-      </c>
-      <c r="P27" s="13" t="inlineStr">
-        <is>
-          <t>4B - Công nghệ</t>
-        </is>
-      </c>
+          <t>1B - GDTC</t>
+        </is>
+      </c>
+      <c r="O27" s="13" t="inlineStr"/>
+      <c r="P27" s="13" t="inlineStr"/>
       <c r="Q27" s="13" t="inlineStr">
         <is>
-          <t>1B - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R27" s="13" t="inlineStr">
-        <is>
-          <t>5A - GDTC</t>
-        </is>
-      </c>
-      <c r="S27" s="13" t="inlineStr">
-        <is>
-          <t>4A - Âm nhạc</t>
-        </is>
-      </c>
+          <t>1A - Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="R27" s="13" t="inlineStr"/>
+      <c r="S27" s="13" t="inlineStr"/>
       <c r="T27" s="13" t="inlineStr"/>
       <c r="U27" s="13" t="inlineStr"/>
       <c r="V27" s="13" t="inlineStr"/>
@@ -4575,43 +4547,43 @@
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr"/>
-      <c r="G28" s="13" t="inlineStr"/>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>2A - HĐTN</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>3A - HĐTN</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr"/>
-      <c r="K28" s="13" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>4B - Tiếng Việt</t>
+        </is>
+      </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr">
-        <is>
-          <t>5B - Đạo đức</t>
-        </is>
-      </c>
+          <t>5A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>1B - Đạo đức</t>
+          <t>1B - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="O28" s="13" t="inlineStr">
         <is>
-          <t>2A - TC Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="P28" s="13" t="inlineStr">
-        <is>
-          <t>4B - LS &amp; ĐL</t>
-        </is>
-      </c>
+          <t>2B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="inlineStr"/>
       <c r="Q28" s="13" t="inlineStr">
         <is>
-          <t>3A - Tiếng Anh</t>
+          <t>5B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R28" s="13" t="inlineStr">
@@ -4639,53 +4611,53 @@
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr"/>
-      <c r="G29" s="13" t="inlineStr"/>
-      <c r="H29" s="13" t="inlineStr"/>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>2A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>2B - Toán</t>
+        </is>
+      </c>
       <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr"/>
-      <c r="K29" s="13" t="inlineStr"/>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="M29" s="13" t="inlineStr">
-        <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>4A - Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>4B - Đạo đức</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="13" t="inlineStr"/>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>2A - Đạo đức</t>
+          <t>1B - TC Toán</t>
         </is>
       </c>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>3A - TC Toán</t>
-        </is>
-      </c>
-      <c r="P29" s="13" t="inlineStr">
-        <is>
-          <t>4A - LS &amp; ĐL</t>
-        </is>
-      </c>
+          <t>3A - Công nghệ</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr"/>
       <c r="Q29" s="13" t="inlineStr">
         <is>
-          <t>2B - Tiếng Anh</t>
+          <t>5A - Tiếng Anh</t>
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr"/>
-      <c r="S29" s="13" t="inlineStr">
-        <is>
-          <t>1B - Âm nhạc</t>
-        </is>
-      </c>
-      <c r="T29" s="13" t="inlineStr"/>
-      <c r="U29" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tin học</t>
-        </is>
-      </c>
+      <c r="S29" s="13" t="inlineStr"/>
+      <c r="T29" s="13" t="inlineStr">
+        <is>
+          <t>5B - Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="U29" s="13" t="inlineStr"/>
       <c r="V29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
@@ -4708,11 +4680,7 @@
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr"/>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>2B - Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="H30" s="13" t="inlineStr"/>
       <c r="I30" s="13" t="inlineStr">
         <is>
           <t>3A - Tiếng Việt</t>
@@ -4720,40 +4688,44 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>4A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr"/>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>4A - Toán</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>4B - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
       <c r="M30" s="13" t="inlineStr"/>
       <c r="N30" s="13" t="inlineStr">
         <is>
-          <t>1A - Tự nhiên &amp; Xã hội</t>
+          <t>1A - TC Toán</t>
         </is>
       </c>
       <c r="O30" s="13" t="inlineStr">
         <is>
-          <t>2A - TC Toán</t>
+          <t>2B - TC Toán</t>
         </is>
       </c>
       <c r="P30" s="13" t="inlineStr">
         <is>
-          <t>5B - Khoa học</t>
-        </is>
-      </c>
-      <c r="Q30" s="13" t="inlineStr">
-        <is>
-          <t>4B - Tiếng Anh</t>
-        </is>
-      </c>
+          <t>5A - Khoa học</t>
+        </is>
+      </c>
+      <c r="Q30" s="13" t="inlineStr"/>
       <c r="R30" s="13" t="inlineStr"/>
-      <c r="S30" s="13" t="inlineStr"/>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>2A - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T30" s="13" t="inlineStr"/>
-      <c r="U30" s="13" t="inlineStr"/>
+      <c r="U30" s="13" t="inlineStr">
+        <is>
+          <t>5B - Tin học</t>
+        </is>
+      </c>
       <c r="V30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
@@ -4775,7 +4747,7 @@
       <c r="H31" s="13" t="inlineStr"/>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>3A - Toán</t>
+          <t>3A - TC Toán</t>
         </is>
       </c>
       <c r="J31" s="13" t="inlineStr">
@@ -4785,7 +4757,7 @@
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>4B - Toán</t>
+          <t>4B - HĐTN</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr"/>
@@ -4797,24 +4769,24 @@
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>2B - TC Toán</t>
-        </is>
-      </c>
-      <c r="P31" s="13" t="inlineStr"/>
-      <c r="Q31" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="R31" s="13" t="inlineStr"/>
-      <c r="S31" s="13" t="inlineStr">
-        <is>
-          <t>5B - Âm nhạc</t>
-        </is>
-      </c>
+          <t>2A - TC Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="inlineStr">
+        <is>
+          <t>5A - LS &amp; ĐL</t>
+        </is>
+      </c>
+      <c r="Q31" s="13" t="inlineStr"/>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>5B - GDTC</t>
+        </is>
+      </c>
+      <c r="S31" s="13" t="inlineStr"/>
       <c r="T31" s="13" t="inlineStr">
         <is>
-          <t>5A - Mỹ thuật</t>
+          <t>2B - Mỹ thuật</t>
         </is>
       </c>
       <c r="U31" s="13" t="inlineStr"/>
@@ -4828,33 +4800,25 @@
           <t>Tiết 7</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr"/>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>2A - GDTC</t>
+        </is>
+      </c>
       <c r="E32" s="13" t="inlineStr"/>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>2A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>2B - HĐTN</t>
-        </is>
-      </c>
+          <t>1B - Toán</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr"/>
+      <c r="H32" s="13" t="inlineStr"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>3A - HĐTN</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>4A - Toán</t>
-        </is>
-      </c>
+          <t>3A - Toán</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr">
         <is>
           <t>4B - Tiếng Việt</t>
@@ -4867,21 +4831,29 @@
           <t>1A - GDTC</t>
         </is>
       </c>
-      <c r="O32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>2B - TC Tiếng Việt</t>
+        </is>
+      </c>
       <c r="P32" s="13" t="inlineStr">
         <is>
-          <t>5B - Khoa học</t>
-        </is>
-      </c>
-      <c r="Q32" s="13" t="inlineStr">
-        <is>
-          <t>5A - Tiếng Anh</t>
-        </is>
-      </c>
+          <t>4A - Khoa học</t>
+        </is>
+      </c>
+      <c r="Q32" s="13" t="inlineStr"/>
       <c r="R32" s="13" t="inlineStr"/>
-      <c r="S32" s="13" t="inlineStr"/>
+      <c r="S32" s="13" t="inlineStr">
+        <is>
+          <t>5B - Âm nhạc</t>
+        </is>
+      </c>
       <c r="T32" s="13" t="inlineStr"/>
-      <c r="U32" s="13" t="inlineStr"/>
+      <c r="U32" s="13" t="inlineStr">
+        <is>
+          <t>5A - Tin học</t>
+        </is>
+      </c>
       <c r="V32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
@@ -4903,17 +4875,13 @@
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>1A - Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>1B - Tiếng Việt</t>
-        </is>
-      </c>
+          <t>1A - HĐTN</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>2A - Toán</t>
+          <t>2A - Tiếng Việt</t>
         </is>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -4923,7 +4891,7 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>3A - Tiếng Việt</t>
+          <t>3A - TC Tiếng Việt</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
@@ -4933,21 +4901,25 @@
       </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>4B - TC Tiếng Việt</t>
+          <t>4B - Toán</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>5A - Toán</t>
-        </is>
-      </c>
-      <c r="M33" s="10" t="inlineStr"/>
+          <t>5A - Đạo đức</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>5B - Toán</t>
+        </is>
+      </c>
       <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="10" t="inlineStr"/>
       <c r="Q33" s="10" t="inlineStr">
         <is>
-          <t>5B - Tiếng Anh</t>
+          <t>1B - Tiếng Anh</t>
         </is>
       </c>
       <c r="R33" s="10" t="inlineStr"/>
@@ -4977,7 +4949,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>2A - Tiếng Việt</t>
+          <t>2A - Toán</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -4987,7 +4959,7 @@
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>3A - TTCM</t>
+          <t>3A - Tiếng Việt</t>
         </is>
       </c>
       <c r="J34" s="10" t="inlineStr">
@@ -4997,18 +4969,18 @@
       </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>4B - Tiếng Việt</t>
+          <t>4B - TC Toán</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>5B - Toán</t>
-        </is>
-      </c>
+      <c r="M34" s="10" t="inlineStr"/>
       <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="10" t="inlineStr"/>
+      <c r="P34" s="10" t="inlineStr">
+        <is>
+          <t>5B - Khoa học</t>
+        </is>
+      </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>5A - Tiếng Anh</t>
@@ -5031,12 +5003,12 @@
       <c r="D35" s="10" t="inlineStr"/>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>1A - Toán</t>
+          <t>1A - Tiếng Việt</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>1B - Toán</t>
+          <t>1B - Tiếng Việt</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -5055,14 +5027,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>4B - Toán</t>
-        </is>
-      </c>
+      <c r="K35" s="10" t="inlineStr"/>
       <c r="L35" s="10" t="inlineStr">
         <is>
-          <t>5A - Đạo đức</t>
+          <t>5A - Toán</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
@@ -5072,7 +5040,11 @@
       </c>
       <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" s="10" t="inlineStr"/>
+      <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>4B - Khoa học</t>
+        </is>
+      </c>
       <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>4A - Tiếng Anh</t>
